--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2020_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2020_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:14</t>
+    <t xml:space="preserve">2026-09-09 23:09</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2020_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2020_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:09</t>
+    <t xml:space="preserve">2026-09-17 14:05</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2020_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2020_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:05</t>
+    <t xml:space="preserve">2026-09-23 12:34</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2020_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2020_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:34</t>
+    <t xml:space="preserve">2026-10-02 13:56</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2020_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2020_biobio.xlsx
@@ -48,7 +48,7 @@
     <t xml:space="preserve">Talcahuano</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Angeles</t>
+    <t xml:space="preserve">Los Ángeles</t>
   </si>
   <si>
     <t xml:space="preserve">Hualpén</t>
@@ -102,7 +102,7 @@
     <t xml:space="preserve">Santa Juana</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Alamos</t>
+    <t xml:space="preserve">Los Álamos</t>
   </si>
   <si>
     <t xml:space="preserve">Quilleco</t>
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:56</t>
+    <t xml:space="preserve">2026-10-04 08:59</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2020_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2020_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 08:59</t>
+    <t xml:space="preserve">2026-10-05 10:41</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -648,7 +648,7 @@
         <v>2020</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>293352.12</v>
+        <v>293352.13</v>
       </c>
     </row>
     <row r="7">
@@ -988,7 +988,7 @@
         <v>2020</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>193450.12</v>
+        <v>193450.13</v>
       </c>
     </row>
     <row r="27">
